--- a/results/bemac/bemac_classA_Ru62_Rv62_SC/bler_vs_N.xlsx
+++ b/results/bemac/bemac_classA_Ru62_Rv62_SC/bler_vs_N.xlsx
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BE-MAC — Class A, (Ru=0.62, Rv=0.62), SC (L=1), mc design</t>
+          <t>BE-MAC — Class A, (Ru=0.62, Rv=0.62), SC (L=1)</t>
         </is>
       </c>
     </row>
